--- a/data/trans_bre/IP1003-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 9,82</t>
+          <t>-1,41; 9,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 7,49</t>
+          <t>-1,69; 7,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 10,84</t>
+          <t>-0,19; 11,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 3,19</t>
+          <t>-8,42; 3,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 546,14</t>
+          <t>-28,29; 472,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-70,16; 1332,38</t>
+          <t>-60,97; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 896,26</t>
+          <t>-27,67; 1252,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,27; 75,89</t>
+          <t>-74,18; 73,15</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 7,76</t>
+          <t>-5,62; 6,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 3,29</t>
+          <t>-5,11; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 1,41</t>
+          <t>-7,02; 1,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 3,91</t>
+          <t>-9,76; 3,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 253,78</t>
+          <t>-59,54; 214,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,27; 234,02</t>
+          <t>-84,36; 249,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,62; 75,18</t>
+          <t>-90,79; 85,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,55; 118,28</t>
+          <t>-79,22; 125,09</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 3,17</t>
+          <t>-9,53; 4,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,41</t>
+          <t>-1,73; 5,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 2,99</t>
+          <t>-8,28; 1,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 8,38</t>
+          <t>-11,97; 7,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,71; 64,46</t>
+          <t>-81,42; 82,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 196,61</t>
+          <t>-100,0; 91,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 362,0</t>
+          <t>-83,28; 216,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 1,3</t>
+          <t>-5,55; 1,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -3,17</t>
+          <t>-11,54; -3,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,3</t>
+          <t>-3,13; 3,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,55</t>
+          <t>-4,45; 4,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,4; 34,87</t>
+          <t>-68,43; 43,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,81; -31,95</t>
+          <t>-85,94; -35,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,1; 110,97</t>
+          <t>-50,41; 127,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,2; 112,16</t>
+          <t>-49,45; 111,34</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 8,23</t>
+          <t>-1,8; 8,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 8,46</t>
+          <t>-1,85; 8,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 5,14</t>
+          <t>-3,52; 5,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -2,27</t>
+          <t>-14,44; -1,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,83; 362,37</t>
+          <t>-33,92; 371,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,53; 290,08</t>
+          <t>-29,15; 262,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,59; 236,15</t>
+          <t>-58,42; 231,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-87,02; -18,15</t>
+          <t>-85,68; -11,01</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 0,87</t>
+          <t>-13,92; 0,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 1,84</t>
+          <t>-7,84; 2,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 2,93</t>
+          <t>-10,74; 2,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 1,96</t>
+          <t>-10,49; 2,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,08; 22,3</t>
+          <t>-88,26; 30,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-91,47; 154,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,08; 69,75</t>
+          <t>-90,79; 80,63</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,51</t>
+          <t>-2,64; 1,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,54</t>
+          <t>-3,48; 0,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,87</t>
+          <t>-1,98; 1,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -0,49</t>
+          <t>-5,42; -0,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 27,52</t>
+          <t>-33,74; 30,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 11,48</t>
+          <t>-50,05; 13,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 50,83</t>
+          <t>-33,91; 51,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-56,56; -6,71</t>
+          <t>-55,89; -4,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 9,4</t>
+          <t>-1,33; 9,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 7,86</t>
+          <t>-1,81; 7,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 11,47</t>
+          <t>-0,15; 10,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 3,25</t>
+          <t>-8,65; 3,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 472,95</t>
+          <t>-30,09; 454,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,97; —</t>
+          <t>-68,04; 934,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 1252,62</t>
+          <t>-19,71; 1564,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 73,15</t>
+          <t>-72,54; 90,82</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 6,92</t>
+          <t>-5,52; 7,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 3,37</t>
+          <t>-5,66; 3,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 1,11</t>
+          <t>-7,08; 1,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 3,7</t>
+          <t>-10,28; 3,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,54; 214,42</t>
+          <t>-56,86; 188,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,36; 249,4</t>
+          <t>-98,7; 196,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,79; 85,94</t>
+          <t>-90,19; 81,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,22; 125,09</t>
+          <t>-82,5; 101,97</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 4,26</t>
+          <t>-10,36; 2,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,86</t>
+          <t>-1,65; 6,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 1,96</t>
+          <t>-7,82; 3,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 7,13</t>
+          <t>-10,89; 8,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,42; 82,43</t>
+          <t>-84,78; 48,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,61</t>
+          <t>-100,0; 248,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-83,28; 216,85</t>
+          <t>-81,07; 270,58</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 1,58</t>
+          <t>-5,68; 1,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,54; -3,22</t>
+          <t>-11,59; -3,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,66</t>
+          <t>-3,05; 3,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 4,55</t>
+          <t>-4,8; 4,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 43,86</t>
+          <t>-70,36; 39,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,94; -35,9</t>
+          <t>-85,81; -35,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 127,05</t>
+          <t>-46,38; 116,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 111,34</t>
+          <t>-53,98; 98,01</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 8,17</t>
+          <t>-1,66; 8,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 8,61</t>
+          <t>-1,58; 8,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 5,55</t>
+          <t>-3,68; 5,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,44; -1,86</t>
+          <t>-13,33; -1,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 371,89</t>
+          <t>-36,96; 372,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 262,46</t>
+          <t>-27,47; 248,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 231,36</t>
+          <t>-56,16; 268,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-85,68; -11,01</t>
+          <t>-85,91; -17,31</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 0,79</t>
+          <t>-13,71; 0,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 2,07</t>
+          <t>-7,96; 2,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 2,7</t>
+          <t>-11,48; 2,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 2,31</t>
+          <t>-10,29; 1,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,26; 30,15</t>
+          <t>-87,59; 27,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,76; 153,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,79; 80,63</t>
+          <t>-89,79; 76,19</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,64</t>
+          <t>-2,63; 1,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,64</t>
+          <t>-3,39; 0,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,8</t>
+          <t>-2,07; 1,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,42; -0,21</t>
+          <t>-5,44; -0,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 30,09</t>
+          <t>-34,21; 30,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 13,01</t>
+          <t>-47,22; 14,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,91; 51,14</t>
+          <t>-35,6; 49,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-55,89; -4,31</t>
+          <t>-54,2; -5,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>-2,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-32,27%</t>
+          <t>-30,41%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 9,24</t>
+          <t>-0,67; 9,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 7,67</t>
+          <t>-1,71; 7,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 10,57</t>
+          <t>0,01; 10,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 3,46</t>
+          <t>-9,86; 3,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 454,4</t>
+          <t>-24,12; 546,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,04; 934,64</t>
+          <t>-70,16; 1332,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 1564,71</t>
+          <t>-39,84; 896,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 90,82</t>
+          <t>-73,63; 79,92</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-36,98%</t>
+          <t>-41,68%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 7,37</t>
+          <t>-5,36; 7,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 3,15</t>
+          <t>-5,52; 3,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 1,15</t>
+          <t>-7,0; 1,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 3,73</t>
+          <t>-10,99; 3,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 188,31</t>
+          <t>-56,56; 253,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-98,7; 196,42</t>
+          <t>-89,27; 234,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,19; 81,56</t>
+          <t>-90,62; 75,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,5; 101,97</t>
+          <t>-85,77; 98,23</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-17,14%</t>
+          <t>-9,36%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 2,43</t>
+          <t>-10,2; 3,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 6,14</t>
+          <t>-1,7; 6,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 3,2</t>
+          <t>-8,03; 2,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 8,34</t>
+          <t>-10,56; 8,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-84,78; 48,9</t>
+          <t>-81,71; 64,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 248,98</t>
+          <t>-100,0; 196,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,07; 270,58</t>
+          <t>-79,07; 354,97</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 1,39</t>
+          <t>-5,71; 1,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -3,21</t>
+          <t>-11,22; -3,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,64</t>
+          <t>-3,32; 3,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 4,5</t>
+          <t>-3,54; 6,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,36; 39,77</t>
+          <t>-68,4; 34,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,81; -35,25</t>
+          <t>-84,81; -31,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,38; 116,6</t>
+          <t>-50,1; 110,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,98; 98,01</t>
+          <t>-38,69; 140,15</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,39</t>
+          <t>-6,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-63,97%</t>
+          <t>-58,17%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 8,44</t>
+          <t>-1,43; 8,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 8,23</t>
+          <t>-1,64; 8,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 5,55</t>
+          <t>-3,74; 5,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -1,73</t>
+          <t>-11,97; -1,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 372,73</t>
+          <t>-25,83; 362,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 248,54</t>
+          <t>-24,53; 290,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 268,64</t>
+          <t>-58,59; 236,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-85,91; -17,31</t>
+          <t>-83,62; -3,53</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,97</t>
+          <t>-4,66</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-52,86%</t>
+          <t>-55,59%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 0,57</t>
+          <t>-13,65; 0,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 2,15</t>
+          <t>-8,25; 1,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 2,49</t>
+          <t>-11,37; 2,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 1,87</t>
+          <t>-12,14; 1,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,59; 27,08</t>
+          <t>-90,08; 22,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-91,76; 153,55</t>
+          <t>-91,47; 154,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-89,79; 76,19</t>
+          <t>-90,86; 53,88</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-34,27%</t>
+          <t>-28,57%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,71</t>
+          <t>-2,93; 1,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,52</t>
+          <t>-3,52; 0,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,93</t>
+          <t>-1,93; 1,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; -0,46</t>
+          <t>-5,34; -0,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 30,4</t>
+          <t>-37,14; 27,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,22; 14,01</t>
+          <t>-49,61; 11,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 49,91</t>
+          <t>-33,34; 50,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-54,2; -5,99</t>
+          <t>-51,5; 0,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,54</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,82</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,69</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>110,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>183,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-30,41%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.123739746444537</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.535525165004025</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>4.82318150831708</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.692100879249631</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.9874971489980788</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.105245688683426</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.839882881439636</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.3040679270763548</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,67; 9,82</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 7,49</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,01; 10,84</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-9,86; 3,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-24,12; 546,14</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-70,16; 1332,38</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-39,84; 896,26</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-73,63; 79,92</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.6666164179428241</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.714701248955154</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.005842920557546466</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-9.859862890129763</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.241247089209647</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7016363763867501</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3983639513771964</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.7363419337107914</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.816707495706609</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.493976863411028</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.83966639790624</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.407896469760369</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>5.461446891550997</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>13.32377116056595</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>8.962644876408111</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.7991675676613429</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,56</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-23,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-48,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-41,68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,36; 7,76</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,52; 3,29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,0; 1,41</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-10,99; 3,51</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-56,56; 253,78</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-89,27; 234,02</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-90,62; 75,18</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-85,77; 98,23</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.88519872679792</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.9417331710211557</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.503440115116744</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.564004736341764</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1321505410357709</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2303889391544708</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.4870408023859691</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4168336397745693</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,42</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,51</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-37,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>103,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-46,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-9,36%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.360891306936056</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.516448297669655</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-6.996892521601472</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-10.99200928114096</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5656448238556911</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8926607551066855</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.9061775518511008</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.8576958404552922</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-10,2; 3,17</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,7; 6,41</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,03; 2,99</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-10,56; 8,83</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-81,71; 64,46</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 196,61</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-79,07; 354,97</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.75908491632057</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.291375389908809</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.410885769535839</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.508782767413979</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.537801791199226</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.340216258221375</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.7517620738823378</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.9823195110944533</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-7,24</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-33,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-67,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19,28%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.420309224055532</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.725454497777724</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.508004260887164</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.7812145895270739</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3712794008515004</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.035087455833809</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4617897728173583</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.09362721757953552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,71; 1,3</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-11,22; -3,17</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,32; 3,3</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,54; 6,02</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-68,4; 34,87</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-84,81; -31,95</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-50,1; 110,97</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-38,69; 140,15</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-10.19646550079513</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.700966929409593</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.031448719309022</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-10.55998090311165</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8170812643159209</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7906950244800747</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.168432111459185</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.407567508794535</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.988927807895578</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8.82943505604036</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.6446100992732878</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n">
+        <v>1.966101210870804</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>3.54967356411924</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,08</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-6,11</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>65,97%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>57,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>22,37%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-58,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,43; 8,23</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,64; 8,46</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,74; 5,14</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-11,97; -1,13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-25,83; 362,37</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-24,53; 290,08</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-58,59; 236,15</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-83,62; -3,53</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-2.110266197256992</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-7.238299043660875</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2988230848496656</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.324250024418973</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3357869969666809</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.6778888838581731</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.06346511568085433</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1927534161855398</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-6,15</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-2,64</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-4,06</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,66</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-55,98%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-63,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-52,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-55,59%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.714512417204891</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-11.2248984171956</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.323100091087059</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.54224470354533</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6839964509630323</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8481331027794606</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5010095837840035</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3869263063258171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-13,65; 0,87</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-8,25; 1,84</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-11,37; 2,93</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-12,14; 1,27</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-90,08; 22,3</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-91,47; 154,99</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-90,86; 53,88</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.298779443367936</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-3.171439963571114</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.301177248246105</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.020491209695576</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3486771099476208</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.3195364650070731</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.109717189389359</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.401470130239846</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1015,293 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,43</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-7,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-23,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-1,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-28,57%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>3.002167857511631</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.078007236615934</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9758490319269147</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-6.114514464371242</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.6596733167223447</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.5708768888848779</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.2236821319437237</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.5817425611790548</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,93; 1,51</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,52; 0,54</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,93; 1,87</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-5,34; -0,04</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-37,14; 27,52</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-49,61; 11,48</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-33,34; 50,83</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-51,5; 0,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.428891259367204</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.635334121987354</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.737329090289172</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-11.96754513261047</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2582985936551169</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2453482771428509</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.5859174938111679</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.8362075446693918</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8.232253057505154</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8.461962219087241</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.13793378024952</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-1.127178147298167</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>3.623672055813528</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.900813547118549</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.361525111877946</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-0.03525628840276976</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-6.15179972453839</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-2.635549764477253</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-4.055974282550601</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-4.663057590130888</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.5598022817786272</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.6345469660554544</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.5253825757904232</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.5558641984942716</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-13.6498848276549</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-8.245333689141306</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-11.36892113113988</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-12.13966746731235</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.9008488337348964</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="n">
+        <v>-0.9146587416764133</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.9086200462041215</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.8684560614336179</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1.841253657848149</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2.930722720773403</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1.272825671325287</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2230161107527511</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="n">
+        <v>1.549911213707349</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.5387898585948867</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.5224917071365555</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-1.388639884654364</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.08973440785662867</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.428963743201757</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.07873560263294806</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.2343705396417178</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.01877898177243542</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.2857000968956723</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.926715066705563</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.522558957409892</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.934514978629583</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-5.340858563766139</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.3714048707369559</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.496097138346402</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.3333890909547387</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.514962765546338</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.506301794687071</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.5422583325408564</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.872539938237036</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.04144880131438586</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.2752256967040376</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.114826108755565</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.508332201738724</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.004360782549437258</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1309,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
